--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104609_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104609_W17.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6326</v>
+        <v>4.5613</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1335</v>
+        <v>1.7533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4992</v>
+        <v>2.808</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9165</v>
+        <v>1.33</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8787</v>
+        <v>1.439</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.1091</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8662</v>
+        <v>1.6119</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7867</v>
+        <v>0.2199</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0795</v>
+        <v>1.392</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9497</v>
+        <v>-0.2819</v>
       </c>
       <c r="N2" t="n">
-        <v>0.092</v>
+        <v>1.2192</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0417</v>
+        <v>-1.5011</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>3.4145</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9015</v>
+        <v>-0.0858</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4014</v>
+        <v>0.2388</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5</v>
+        <v>-0.3246</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0358</v>
+        <v>3.2618</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1513</v>
+        <v>1.2509</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8845</v>
+        <v>2.0109</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1786</v>
+        <v>1.1772</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7299</v>
+        <v>1.7232</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7611</v>
+        <v>1.7345</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1469</v>
+        <v>-1.1623</v>
       </c>
       <c r="L3" t="n">
-        <v>2.908</v>
+        <v>2.8968</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5825</v>
+        <v>-0.5573</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5956</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4962</v>
+        <v>0.7188</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5243</v>
+        <v>0.6546</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0281</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0264</v>
+        <v>3.2499</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3881</v>
+        <v>1.1633</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6383</v>
+        <v>2.0866</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3402</v>
+        <v>0.645</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4416</v>
+        <v>-0.5749</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1014</v>
+        <v>1.2198</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6586</v>
+        <v>1.9325</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2487</v>
+        <v>-0.8898</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4099</v>
+        <v>2.8223</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3184</v>
+        <v>-1.2876</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1929</v>
+        <v>0.3149</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5113</v>
+        <v>-1.6025</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6333</v>
+        <v>-0.8699</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1875</v>
+        <v>-0.8296</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4458</v>
+        <v>-0.0403</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1853</v>
+        <v>2.3367</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>2.3367</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8682</v>
+        <v>3.2266</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8485</v>
+        <v>2.5946</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0197</v>
+        <v>0.632</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6404</v>
+        <v>0.9192</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5831</v>
+        <v>1.8784</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2234</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9533</v>
+        <v>2.8369</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.88</v>
+        <v>1.7647</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8334</v>
+        <v>1.0722</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.313</v>
+        <v>-1.9177</v>
       </c>
       <c r="N5" t="n">
-        <v>0.297</v>
+        <v>0.1137</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6099</v>
+        <v>-2.0314</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4025</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2524</v>
+        <v>0.4863</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1825</v>
+        <v>0.8959</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0699</v>
+        <v>-0.4096</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1326</v>
+        <v>0.7664</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7962</v>
+        <v>0.5062</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3364</v>
+        <v>0.2602</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0217</v>
+        <v>-1.0163</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.446</v>
+        <v>-0.4398</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5758</v>
+        <v>-0.5765</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.22</v>
+        <v>-0.2298</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8017</v>
+        <v>-0.7865</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0201</v>
+        <v>0.6445</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0162</v>
+        <v>0.736</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0039</v>
+        <v>-0.0915</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8359</v>
+        <v>0.4429</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1715</v>
+        <v>-1.1771</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0074</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>0.082</v>
+        <v>0.0955</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2899</v>
+        <v>0.301</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2079</v>
+        <v>-0.2055</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3105</v>
+        <v>0.3096</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2285</v>
+        <v>-0.2141</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3003</v>
+        <v>-0.1078</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6481</v>
+        <v>0.2407</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4036</v>
+        <v>-0.1486</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0672</v>
+        <v>0.1205</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3364</v>
+        <v>-0.2691</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1862</v>
+        <v>-0.1812</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1946</v>
+        <v>0.1952</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4119</v>
+        <v>-0.1626</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1391</v>
+        <v>0.0487</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0511</v>
+        <v>-0.7101</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1328</v>
+        <v>-0.3809</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0818</v>
+        <v>-0.3293</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9251</v>
+        <v>-1.0096</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4991</v>
+        <v>1.7689</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.426</v>
+        <v>-2.7785</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.1344</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0999</v>
+        <v>1.4684</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1893</v>
+        <v>-1.334</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8357</v>
+        <v>-1.1441</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.599</v>
+        <v>0.3005</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2368</v>
+        <v>-1.4446</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1674</v>
+        <v>-0.8386</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0434</v>
+        <v>-0.2374</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.124</v>
+        <v>-0.6012</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.26</v>
+        <v>-0.7501</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6494</v>
+        <v>-0.8541</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6106</v>
+        <v>0.104</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2128</v>
+        <v>-1.9346</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1457</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9329</v>
+        <v>-1.424</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5544</v>
+        <v>-0.1151</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7517</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3061</v>
+        <v>-0.1939</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7672</v>
+        <v>-1.8194</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.394</v>
+        <v>-0.5893</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3732</v>
+        <v>-1.2301</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.206</v>
+        <v>-0.8642</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0696</v>
+        <v>-0.7389</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1364</v>
+        <v>-0.1253</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.979</v>
+        <v>-1.2283</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4228</v>
+        <v>-0.6597</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5562</v>
+        <v>-0.5686</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0064</v>
+        <v>-0.2123</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7632</v>
+        <v>-1.1432</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7696</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1652</v>
+        <v>0.5481</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4821</v>
+        <v>-0.7552</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3169</v>
+        <v>1.3033</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1716</v>
+        <v>-0.7604</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2811</v>
+        <v>-0.3881</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4526</v>
+        <v>-0.3724</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1068</v>
+        <v>-0.1754</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3217</v>
+        <v>-0.0697</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7852</v>
+        <v>-0.1057</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8678</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4674</v>
+        <v>-1.6019</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4125</v>
+        <v>-2.4599</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.858</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7976</v>
+        <v>-3.818</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0245</v>
+        <v>1.0226</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.8221</v>
+        <v>-4.8406</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9383</v>
+        <v>-1.9857</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2153</v>
+        <v>1.1958</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.1535</v>
+        <v>-3.1816</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8593</v>
+        <v>-1.8323</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3749</v>
+        <v>-0.4879</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3912</v>
+        <v>-0.3768</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0163</v>
+        <v>-0.1111</v>
       </c>
       <c r="V12" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.3704</v>
+        <v>11.0699</v>
       </c>
       <c r="E13" t="n">
-        <v>1.461399999999999</v>
+        <v>1.8571</v>
       </c>
       <c r="F13" t="n">
-        <v>8.9092</v>
+        <v>9.2127</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.797500000000001</v>
+        <v>-3.809899999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9865</v>
+        <v>3.0142</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.7842</v>
+        <v>-6.824300000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>7.0936</v>
+        <v>6.849</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5102</v>
+        <v>1.3719</v>
       </c>
       <c r="L13" t="n">
-        <v>5.583499999999998</v>
+        <v>5.476899999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.8912</v>
+        <v>-10.6591</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4764</v>
+        <v>1.642299999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.3675</v>
+        <v>-12.3014</v>
       </c>
       <c r="P13" t="n">
-        <v>10.2077</v>
+        <v>10.2437</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R13" t="n">
-        <v>22.6833</v>
+        <v>22.7632</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4346</v>
+        <v>-1.7426</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7409000000000001</v>
+        <v>-0.02689999999999992</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6939</v>
+        <v>-1.7157</v>
       </c>
       <c r="V13" t="n">
-        <v>6.395299999999999</v>
+        <v>6.379</v>
       </c>
       <c r="W13" t="n">
-        <v>7.584499999999999</v>
+        <v>7.5548</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1892</v>
+        <v>-1.1759</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3721</v>
+        <v>7.3151</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7248</v>
+        <v>5.369</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6472</v>
+        <v>1.9461</v>
       </c>
       <c r="G14" t="n">
-        <v>8.190300000000001</v>
+        <v>8.182399999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8543</v>
+        <v>1.8471</v>
       </c>
       <c r="I14" t="n">
-        <v>6.336</v>
+        <v>6.3353</v>
       </c>
       <c r="J14" t="n">
-        <v>8.972200000000001</v>
+        <v>8.9221</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1086</v>
+        <v>2.0782</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8636</v>
+        <v>6.8439</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.782</v>
+        <v>-0.7396</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2543</v>
+        <v>-0.231</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5276</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0035</v>
+        <v>-0.0463</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9376</v>
+        <v>-0.2281</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.066</v>
+        <v>0.1818</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3565</v>
+        <v>2.9151</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1808</v>
+        <v>0.7371</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1757</v>
+        <v>2.1779</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8373</v>
+        <v>1.8363</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0287</v>
+        <v>-0.0396</v>
       </c>
       <c r="I15" t="n">
-        <v>1.866</v>
+        <v>1.8759</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4262</v>
+        <v>0.3985</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3574</v>
+        <v>-0.3834</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4111</v>
+        <v>1.4377</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>2.317</v>
+        <v>0.8724</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8207</v>
+        <v>0.4085</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4963</v>
+        <v>0.4639</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. DEKKER</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4323</v>
+        <v>1.6729</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4786</v>
+        <v>1.6835</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9538</v>
+        <v>-0.0106</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5919</v>
+        <v>1.6588</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5786</v>
+        <v>0.9732</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0133</v>
+        <v>0.6856</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7568</v>
+        <v>1.5539</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3117</v>
+        <v>1.003</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4451</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1649</v>
+        <v>0.1049</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2669</v>
+        <v>-0.0298</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4318</v>
+        <v>0.1347</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.16</v>
+        <v>-0.4215</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0514</v>
+        <v>0.1297</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2114</v>
+        <v>-0.5512</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>S. DEKKER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1185</v>
+        <v>1.4677</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1352</v>
+        <v>0.4706</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2537</v>
+        <v>0.997</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3352</v>
+        <v>0.5931</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9252</v>
+        <v>0.5828</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.41</v>
+        <v>0.0103</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7159</v>
+        <v>0.7494</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5612</v>
+        <v>0.3103</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1547</v>
+        <v>0.4392</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6193</v>
+        <v>-0.1563</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3639</v>
+        <v>0.2725</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2554</v>
+        <v>-0.4289</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4141</v>
+        <v>0.1917</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0344</v>
+        <v>-0.0512</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3797</v>
+        <v>0.2429</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.174</v>
+        <v>-0.0101</v>
       </c>
       <c r="E18" t="n">
-        <v>0.755</v>
+        <v>-0.6187</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.581</v>
+        <v>0.6086</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6423</v>
+        <v>-2.3172</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9651999999999999</v>
+        <v>-0.9112</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6771</v>
+        <v>-1.406</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5716</v>
+        <v>-0.7298</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0146</v>
+        <v>-0.5656</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.1643</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0707</v>
+        <v>-1.5874</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0494</v>
+        <v>-0.3457</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1201</v>
+        <v>-1.2417</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8954</v>
+        <v>1.2568</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8166</v>
+        <v>0.5664</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0788</v>
+        <v>0.6905</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7071</v>
+        <v>-0.3155</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7071</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5699</v>
+        <v>-0.9244</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4651</v>
+        <v>-0.8284</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1048</v>
+        <v>-0.0961</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4069</v>
+        <v>0.4112</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8485</v>
+        <v>-0.8446</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2555</v>
+        <v>1.2558</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3878</v>
+        <v>0.3819</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0192</v>
+        <v>0.0292</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3841</v>
+        <v>0.0302</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5081</v>
+        <v>0.1555</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.124</v>
+        <v>-0.1253</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2045</v>
+        <v>-2.8045</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2061</v>
+        <v>-0.918</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9985</v>
+        <v>-1.8865</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6958</v>
+        <v>-2.6892</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6536</v>
+        <v>-1.6543</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0422</v>
+        <v>-1.035</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3795</v>
+        <v>-1.3869</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3162</v>
+        <v>-1.3023</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9034</v>
+        <v>0.2914</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1735</v>
+        <v>0.4689</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2701</v>
+        <v>-0.1775</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2201</v>
+        <v>-3.2343</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9247</v>
+        <v>-2.829</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2954</v>
+        <v>-0.4053</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0984</v>
+        <v>1.1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4054</v>
+        <v>0.4104</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6895</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2792</v>
+        <v>1.2708</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3117</v>
+        <v>0.3103</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1808</v>
+        <v>-0.1708</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0502</v>
+        <v>-0.058</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2976</v>
+        <v>0.1721</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9464</v>
+        <v>-4.5983</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0475</v>
+        <v>-3.8247</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8989</v>
+        <v>-0.7736</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7228</v>
+        <v>2.298</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2115</v>
+        <v>0.0485</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5113</v>
+        <v>2.2495</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6612</v>
+        <v>1.908</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4075</v>
+        <v>0.1207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7463</v>
+        <v>1.7874</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0615</v>
+        <v>0.39</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.0722</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2576</v>
+        <v>0.4622</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-5.6908</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7764</v>
+        <v>-0.3436</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1089</v>
+        <v>-0.0419</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6675</v>
+        <v>-0.3017</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0786</v>
+        <v>-5.3845</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0366</v>
+        <v>-2.986</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.042</v>
+        <v>-2.3985</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2862</v>
+        <v>-3.748</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0417</v>
+        <v>-2.2469</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2444</v>
+        <v>-1.5011</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9124</v>
+        <v>-0.7116</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1212</v>
+        <v>-1.4563</v>
       </c>
       <c r="L23" t="n">
-        <v>1.7912</v>
+        <v>0.7447</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3737</v>
+        <v>-3.0364</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0795</v>
+        <v>-0.7906</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4532</v>
+        <v>-2.2458</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.444</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.6708</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8280999999999999</v>
+        <v>0.3635</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2782</v>
+        <v>0.2296</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5498</v>
+        <v>0.1339</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.8043</v>
+        <v>-6.7875</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2332</v>
+        <v>-5.4682</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5711</v>
+        <v>-1.3194</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5019</v>
+        <v>-3.5152</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1642</v>
+        <v>-1.1796</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3377</v>
+        <v>-2.3356</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6585</v>
+        <v>-1.6974</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8321</v>
+        <v>-0.8628</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8434</v>
+        <v>-1.8179</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7431</v>
+        <v>0.3031</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5202</v>
+        <v>0.3085</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2229</v>
+        <v>-0.0055</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W24" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.3704</v>
+        <v>-10.3728</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.9092</v>
+        <v>-9.212800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4613</v>
+        <v>-1.1604</v>
       </c>
       <c r="G25" t="n">
-        <v>3.797600000000001</v>
+        <v>3.810199999999997</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.986499999999999</v>
+        <v>-3.0142</v>
       </c>
       <c r="I25" t="n">
-        <v>6.7841</v>
+        <v>6.824200000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>10.8911</v>
+        <v>10.6589</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4763</v>
+        <v>-1.6422</v>
       </c>
       <c r="L25" t="n">
-        <v>12.3674</v>
+        <v>12.3013</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.093399999999999</v>
+        <v>-6.8489</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.51</v>
+        <v>-1.3719</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.5835</v>
+        <v>-5.4771</v>
       </c>
       <c r="P25" t="n">
-        <v>-10.2074</v>
+        <v>-10.2433</v>
       </c>
       <c r="Q25" t="n">
-        <v>-22.6834</v>
+        <v>-22.763</v>
       </c>
       <c r="R25" t="n">
-        <v>12.4758</v>
+        <v>12.5197</v>
       </c>
       <c r="S25" t="n">
-        <v>2.434699999999999</v>
+        <v>2.4397</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6938</v>
+        <v>1.7158</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7408999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.3955</v>
+        <v>-6.3792</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1892</v>
+        <v>1.1758</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.584699999999999</v>
+        <v>-7.555000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104609_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104609_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-1.1759</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104609_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.555000000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
